--- a/Reports/Top_10_Report.xlsx
+++ b/Reports/Top_10_Report.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mohit Kumar</t>
+          <t xml:space="preserve">Mohit Kumar </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -504,7 +504,7 @@
         <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>98.57142857142858</v>
+        <v>97.54098360655738</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -514,23 +514,23 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Shivangi Pandey</t>
+          <t>Vibhu</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>shivangipandeyabc@gmail.com</t>
+          <t>vibhubtech23-27@liet.in</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>95.58823529411765</v>
+        <v>96</v>
       </c>
       <c r="E4" t="n">
-        <v>97.14285714285714</v>
+        <v>97.54098360655738</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -544,23 +544,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>chetan gooswami</t>
+          <t xml:space="preserve">Shivangi Pandey </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>chetangoswami2006@gmail.com</t>
+          <t>shivangipandeyabc@gmail.com</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>93.75</v>
+        <v>95.58823529411765</v>
       </c>
       <c r="E5" t="n">
-        <v>95.71428571428572</v>
+        <v>95.08196721311475</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>O</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
         <v>93.44262295081968</v>
       </c>
       <c r="E6" t="n">
-        <v>94.28571428571428</v>
+        <v>93.44262295081968</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amrendra Ram Tripathi</t>
+          <t xml:space="preserve">Amrendra Ram Tripathi </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -608,7 +608,7 @@
         <v>93.33333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>92.85714285714286</v>
+        <v>91.80327868852459</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -627,14 +627,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>chetangoswamibtech23-27@liet.in</t>
+          <t>chetangoswami2006@gmail.com</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>93.04347826086956</v>
+        <v>93.12977099236642</v>
       </c>
       <c r="E8" t="n">
-        <v>91.42857142857143</v>
+        <v>90.1639344262295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -648,15 +648,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karan Sharma </t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t xml:space="preserve">Ansh Tyagi </t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>anshtyagi189@gmail.com</t>
+        </is>
+      </c>
       <c r="D9" t="n">
-        <v>92.6829268292683</v>
+        <v>92.19858156028369</v>
       </c>
       <c r="E9" t="n">
-        <v>90</v>
+        <v>88.52459016393442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -670,19 +674,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ansh Tyagi</t>
+          <t>Ritesh Kumar Singh</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>anshtyagi189@gmail.com</t>
+          <t>riteshkumar07.com@gmail.com</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>92.19858156028369</v>
+        <v>92.10526315789474</v>
       </c>
       <c r="E10" t="n">
-        <v>88.57142857142857</v>
+        <v>86.88524590163934</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -696,19 +700,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ritesh Kumar Singh</t>
+          <t xml:space="preserve">Kanak Gupta </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>riteshkumar07.com@gmail.com</t>
+          <t>kanak.gup1234@gmail.com</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>92.10526315789474</v>
+        <v>91.30434782608695</v>
       </c>
       <c r="E11" t="n">
-        <v>87.14285714285714</v>
+        <v>85.24590163934425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
